--- a/Result/profitability/3581.xlsx
+++ b/Result/profitability/3581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.175</v>
+        <v>0.27625</v>
       </c>
       <c r="N2" t="n">
-        <v>32.875</v>
+        <v>31.9125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06750000000000003</v>
+        <v>-0.06375000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>29.48375</v>
+        <v>28.88125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.21625</v>
+        <v>-0.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>28.81875</v>
+        <v>28.08125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.26625</v>
+        <v>-0.14125</v>
       </c>
       <c r="N5" t="n">
-        <v>27.98</v>
+        <v>27.7325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.21875</v>
+        <v>-0.23125</v>
       </c>
       <c r="N6" t="n">
-        <v>27.605</v>
+        <v>27.2325</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3412500000000001</v>
+        <v>-0.3462500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>26.8625</v>
+        <v>26.6175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8560,6 +8560,133 @@
       </c>
       <c r="AM64" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>440</v>
+      </c>
+      <c r="D65" t="n">
+        <v>308</v>
+      </c>
+      <c r="E65" t="n">
+        <v>132</v>
+      </c>
+      <c r="F65" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="G65" t="n">
+        <v>27</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6.12%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>26</v>
+      </c>
+      <c r="J65" t="n">
+        <v>53</v>
+      </c>
+      <c r="K65" t="n">
+        <v>32</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N65" t="n">
+        <v>33.8475</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.032258064516129</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.1593267882187939</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-2.702702702702703</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>-0.06197183098591552</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
